--- a/xls/square_12_tri3_11.xlsx
+++ b/xls/square_12_tri3_11.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>1.1511678245663377</v>
+        <v>1.1511681590580163</v>
       </c>
       <c r="J11">
-        <v>-1.6366749620234111</v>
+        <v>-1.6366746892725808</v>
       </c>
       <c r="K11">
-        <v>-0.5912880631211883</v>
+        <v>-0.5912879476262691</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -517,13 +517,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-2.101409825322417</v>
+        <v>-2.1014097196452446</v>
       </c>
       <c r="J12">
-        <v>-1.8203082400448107</v>
+        <v>-1.8203081412170752</v>
       </c>
       <c r="K12">
-        <v>-1.3276700832830912</v>
+        <v>-1.32767007355104</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-2.091940684388683</v>
+        <v>-2.091940661398343</v>
       </c>
       <c r="J13">
-        <v>-1.8174720911207698</v>
+        <v>-1.817472222740497</v>
       </c>
       <c r="K13">
-        <v>0.94561045762597</v>
+        <v>0.945610051170836</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-2.0425273883086756</v>
+        <v>-2.0425269819887455</v>
       </c>
       <c r="J14">
-        <v>-1.6588430486587575</v>
+        <v>-1.6588428849385481</v>
       </c>
       <c r="K14">
-        <v>1.2604935262893175</v>
+        <v>1.2604916307010428</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-1.2304526725709621</v>
+        <v>-1.2304526275295236</v>
       </c>
       <c r="J15">
-        <v>-0.9297958369985924</v>
+        <v>-0.9297958104793582</v>
       </c>
       <c r="K15">
-        <v>3.5709537454991973</v>
+        <v>3.570953747673467</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-0.05685869163925022</v>
+        <v>-0.05685869201939593</v>
       </c>
       <c r="J16">
-        <v>-0.04741859127629882</v>
+        <v>-0.04741859151794353</v>
       </c>
       <c r="K16">
-        <v>3.709964532378097</v>
+        <v>3.7099645331810307</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>0.00036325355628838625</v>
+        <v>0.00036325355387062245</v>
       </c>
       <c r="J17">
-        <v>0.00014345358186813406</v>
+        <v>0.000143453580743232</v>
       </c>
       <c r="K17">
-        <v>2.463327199879527</v>
+        <v>2.4633271986936043</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>5.70053703169278e-6</v>
+        <v>5.700537036032196e-6</v>
       </c>
       <c r="J18">
-        <v>-1.052591582294597e-5</v>
+        <v>-1.0525915822415576e-5</v>
       </c>
       <c r="K18">
-        <v>2.199311098301443</v>
+        <v>2.1993110982747868</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-8.842088680430764e-6</v>
+        <v>-8.842088688097323e-6</v>
       </c>
       <c r="J19">
-        <v>-1.6117272511600093e-5</v>
+        <v>-1.61172725156022e-5</v>
       </c>
       <c r="K19">
-        <v>2.174262312286525</v>
+        <v>2.174262312094913</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-1.946874647575226e-6</v>
+        <v>-1.9468746484913412e-6</v>
       </c>
       <c r="J20">
-        <v>-1.4836681691753415e-5</v>
+        <v>-1.4836681691464106e-5</v>
       </c>
       <c r="K20">
-        <v>2.197469207213105</v>
+        <v>2.1974692071938264</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>2.660822304078104e-5</v>
+        <v>2.660822303933464e-5</v>
       </c>
       <c r="J21">
-        <v>7.740778867925822e-6</v>
+        <v>7.740778867540096e-6</v>
       </c>
       <c r="K21">
-        <v>2.025288839185949</v>
+        <v>2.025288839214985</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -867,13 +867,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-1.6523785636362472e-5</v>
+        <v>-1.6523785633614033e-5</v>
       </c>
       <c r="J22">
-        <v>-9.937787477118629e-6</v>
+        <v>-9.937787475816758e-6</v>
       </c>
       <c r="K22">
-        <v>1.638207125108948</v>
+        <v>1.638207125321131</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -902,13 +902,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-1.2811734086221651e-7</v>
+        <v>-1.2811734095864928e-7</v>
       </c>
       <c r="J23">
-        <v>-1.4226849837735542e-7</v>
+        <v>-1.4226849857022099e-7</v>
       </c>
       <c r="K23">
-        <v>1.0604000971472163</v>
+        <v>1.060400097374565</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -940,10 +940,290 @@
         <v>-4.21214607826251e-7</v>
       </c>
       <c r="J24">
-        <v>-3.3935466002277893e-7</v>
+        <v>-3.393546602156446e-7</v>
       </c>
       <c r="K24">
-        <v>1.14319534628377</v>
+        <v>1.1431953460865423</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>144</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>-2.4246392440528966e-7</v>
+      </c>
+      <c r="J25">
+        <v>-1.9483203061313368e-7</v>
+      </c>
+      <c r="K25">
+        <v>1.0287198490330787</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>144</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-2.4444086311744916e-7</v>
+      </c>
+      <c r="J26">
+        <v>-2.0376545389913971e-7</v>
+      </c>
+      <c r="K26">
+        <v>1.0481902525291389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-2.1892256063400525e-7</v>
+      </c>
+      <c r="J27">
+        <v>-1.816735782660861e-7</v>
+      </c>
+      <c r="K27">
+        <v>1.0241024323530137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>144</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-2.095518427183606e-7</v>
+      </c>
+      <c r="J28">
+        <v>-1.7430777450510584e-7</v>
+      </c>
+      <c r="K28">
+        <v>1.0154855039627155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>144</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-2.0596643430769326e-7</v>
+      </c>
+      <c r="J29">
+        <v>-1.7112627708060659e-7</v>
+      </c>
+      <c r="K29">
+        <v>1.0103615306753764</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>144</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-1.9775219178077e-7</v>
+      </c>
+      <c r="J30">
+        <v>-1.6248969033790511e-7</v>
+      </c>
+      <c r="K30">
+        <v>0.9962063981908793</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-2.1109226821157106e-7</v>
+      </c>
+      <c r="J31">
+        <v>-1.7412994174490026e-7</v>
+      </c>
+      <c r="K31">
+        <v>1.0110774170262098</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>144</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-1.7267065598884235e-7</v>
+      </c>
+      <c r="J32">
+        <v>-1.459393098313965e-7</v>
+      </c>
+      <c r="K32">
+        <v>0.9842125029438161</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_11.xlsx
+++ b/xls/square_12_tri3_11.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>169</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>486</v>
+      </c>
+      <c r="I9">
+        <v>7.2320421366812235</v>
+      </c>
+      <c r="J9">
+        <v>2.5626852332135934</v>
+      </c>
+      <c r="K9">
+        <v>3.009501574719213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>144</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>169</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>600</v>
+      </c>
+      <c r="I10">
+        <v>4.584435976871432</v>
+      </c>
+      <c r="J10">
+        <v>0.7562134055541038</v>
+      </c>
+      <c r="K10">
+        <v>1.6980310585017973</v>
+      </c>
+    </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
